--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Recetas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,18 +424,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,42 +452,47 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Hecha por</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Tiempo (min)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Raciones</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ingredientes</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Pasos</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Favorita</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Última modificación</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Recetas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,7 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy hh:mm"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -56,9 +59,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -491,8 +500,50 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Prueba</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Principales</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Antonio</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1. Pon el pollo a la plancha</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>46301.34361461805</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:J2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prueba</t>
+          <t>Muslo de pollo con emulsión de limón</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -524,12 +524,15 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Pollo</t>
+          <t>Muslo de pollo
+Limón
+Sal</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. Pon el pollo a la plancha</t>
+          <t>1. Pon el pollo a la plancha a fuego medio
+2. Echa limón y sal al gusto</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -539,7 +542,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>46301.34361461805</v>
+        <v>46301.34431684028</v>
       </c>
     </row>
   </sheetData>

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -535,14 +535,18 @@
 2. Echa limón y sal al gusto</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Los envidiosos dirán que no es emulsión</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>46301.34431684028</v>
+        <v>46301.40270726852</v>
       </c>
     </row>
   </sheetData>

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Recetas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -503,54 +503,109 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Fiambre de pollo</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Desayunos</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1 pechuga pollo
+2 cucharadas aceite de oliva
+2 cucharadas pimentón dulce
+1 cucharada pequeña de sal
+1 cucharada de ajo en polvo
+1 cucharada de tomillo
+1 cucharada de orégano
+Pimienta negra (al gusto)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1. Mezclar en un bol todas las especias junto con el aceite
+2. Untar la pechuga de pollo con la mezcla y dejar reposar en un tupper al menos una hora
+3. Envolver la pechuga en papel de horno
+4. Calentar el horno a 180 grados y hornear la pechuga 30 minutos por un lado y 10 por el otro
+5. Cuando esté listo, córtala en láminas muy finas y consérvala en un tupper</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Échale un chorro de limón una vez cortado</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>46301.42774069445</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>Muslo de pollo con emulsión de limón</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Principales</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Antonio</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D3" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Muslo de pollo
 Limón
 Sal</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Pon el pollo a la plancha a fuego medio
 2. Echa limón y sal al gusto</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Los envidiosos dirán que no es emulsión</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>46301.40270726852</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J2"/>
+  <autoFilter ref="A1:J3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Recetas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Menú semanal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$3</definedName>
@@ -59,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -68,6 +69,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -608,4 +610,116 @@
   <autoFilter ref="A1:J3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Desayuno</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Comida</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Cena</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Menú semanal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -560,54 +560,90 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>Mousse de oreo con galleta María</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Postres</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Antonio</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DOER-GjCHru/?stkn=MWNjZjIwY2x4MXdtcQ==</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>46301.48370234953</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>Muslo de pollo con emulsión de limón</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Principales</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Antonio</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D4" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Muslo de pollo
 Limón
 Sal</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Pon el pollo a la plancha a fuego medio
 2. Echa limón y sal al gusto</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Los envidiosos dirán que no es emulsión</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>46301.40270726852</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J3"/>
+  <autoFilter ref="A1:J4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -577,8 +577,16 @@
         <v>15</v>
       </c>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>14 galletas maria</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1. Triturar galletas María</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/reel/DOER-GjCHru/?stkn=MWNjZjIwY2x4MXdtcQ==</t>
@@ -590,7 +598,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>46301.48370234953</v>
+        <v>46301.48445444444</v>
       </c>
     </row>
     <row r="4">

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -579,12 +579,20 @@
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>14 galletas maria</t>
+          <t>14 galletas maria
+Vaso de leche
+Paquete galletas oreo
+Nata de montar</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. Triturar galletas María</t>
+          <t>1. Meter galletas María y vaso de leche caliente  en trituradora
+2. Triturar
+3. Metemos la mezcla en la nevera
+4. En un recipiente de montar nata, trituramos las galletas oreo con la mano y añadimos nata hasta que cubra. Trituramos y montamos
+5. Servimos encima de la mezcla de galleta María.
+6. Hacemos polvo otras galletas oreo y servimos encima</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -598,7 +606,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>46301.48445444444</v>
+        <v>46301.48902870371</v>
       </c>
     </row>
     <row r="4">

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Menú semanal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -609,57 +609,8 @@
         <v>46301.48902870371</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Muslo de pollo con emulsión de limón</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Principales</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Antonio</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Muslo de pollo
-Limón
-Sal</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Pon el pollo a la plancha a fuego medio
-2. Echa limón y sal al gusto</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Los envidiosos dirán que no es emulsión</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>46301.40270726852</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J4"/>
+  <autoFilter ref="A1:J3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Menú semanal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -505,24 +505,85 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fiambre de pollo</t>
+          <t>Guiso de patatas con magro</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Desayunos</t>
+          <t>Comidas</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>María</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>•	1 cebolla
+•	1 puerro
+•	1-2 dientes de ajo
+•	50 g de aceite de oliva
+•	300 g de magro de cerdo en dados
+•	100 g de tomate frito
+•	1 hoja de laurel
+•	1 cucharadita de pimentón
+•	100 ml de vino blanco
+•	500-600 ml de agua
+•	1 pastilla de caldo
+•	600 g de patatas en trozos
+•	2 zanahorias en rodajas
+•	100 g de guisantes en conserva</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1. 1.	Pica fina la cebolla, el puerro y el ajo. Sofríelos en una cazuela con el aceite a fuego medio unos 5 minutos, removiendo.
+2. 2.	Añade el magro, el tomate frito y el laurel. Aparta la cazuela del fuego un momento, echa el pimentón y remueve para que no se queme. Rehoga 5 minutos.
+3. 3.	Vierte el vino y deja que evapore un par de minutos. Añade el agua y la pastilla de caldo, y cuece tapado a fuego suave unos 15-20 minutos para que el magro empiece a ablandarse.
+4. 4.	Incorpora las patatas y las zanahorias, con más agua si hace falta para cubrirlas. Cuece tapado a fuego suave 20-25 minutos más, hasta que estén tiernas.
+5. 5.	Añade los guisantes escurridos, mezcla con cuidado y deja 2-3 minutos. Rectifica de sal y sirve.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Sustituto de la pastilla de caldo: usa 500-600 ml de caldo casero o de brik en lugar del agua y de la pastilla. Si no tienes caldo, sirve agua con una pizca extra de sal, una cucharadita de pimentón y el laurel</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>46301.58943972222</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Fiambre de pollo</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Desayunos</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1 pechuga pollo
 2 cucharadas aceite de oliva
@@ -534,7 +595,7 @@
 Pimienta negra (al gusto)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Mezclar en un bol todas las especias junto con el aceite
 2. Untar la pechuga de pollo con la mezcla y dejar reposar en un tupper al menos una hora
@@ -543,41 +604,41 @@
 5. Cuando esté listo, córtala en láminas muy finas y consérvala en un tupper</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Échale un chorro de limón una vez cortado</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>46301.42774069445</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Mousse de oreo con galleta María</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Postres</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Antonio</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D4" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>14 galletas maria
 Vaso de leche
@@ -585,7 +646,7 @@
 Nata de montar</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Meter galletas María y vaso de leche caliente  en trituradora
 2. Triturar
@@ -595,22 +656,22 @@
 6. Hacemos polvo otras galletas oreo y servimos encima</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/reel/DOER-GjCHru/?stkn=MWNjZjIwY2x4MXdtcQ==</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>46301.48902870371</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J3"/>
+  <autoFilter ref="A1:J4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -524,29 +524,29 @@
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>•	1 cebolla
-•	1 puerro
-•	1-2 dientes de ajo
-•	50 g de aceite de oliva
-•	300 g de magro de cerdo en dados
-•	100 g de tomate frito
-•	1 hoja de laurel
-•	1 cucharadita de pimentón
-•	100 ml de vino blanco
-•	500-600 ml de agua
-•	1 pastilla de caldo
-•	600 g de patatas en trozos
-•	2 zanahorias en rodajas
-•	100 g de guisantes en conserva</t>
+          <t>1 cebolla
+1 puerro
+1-2 dientes de ajo
+50 g de aceite de oliva
+300 g de magro de cerdo en dados
+100 g de tomate frito
+1 hoja de laurel
+1 cucharadita de pimentón
+100 ml de vino blanco
+500-600 ml de agua
+1 pastilla de caldo
+600 g de patatas en trozos
+2 zanahorias en rodajas
+100 g de guisantes en conserva</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. 1.	Pica fina la cebolla, el puerro y el ajo. Sofríelos en una cazuela con el aceite a fuego medio unos 5 minutos, removiendo.
-2. 2.	Añade el magro, el tomate frito y el laurel. Aparta la cazuela del fuego un momento, echa el pimentón y remueve para que no se queme. Rehoga 5 minutos.
-3. 3.	Vierte el vino y deja que evapore un par de minutos. Añade el agua y la pastilla de caldo, y cuece tapado a fuego suave unos 15-20 minutos para que el magro empiece a ablandarse.
-4. 4.	Incorpora las patatas y las zanahorias, con más agua si hace falta para cubrirlas. Cuece tapado a fuego suave 20-25 minutos más, hasta que estén tiernas.
-5. 5.	Añade los guisantes escurridos, mezcla con cuidado y deja 2-3 minutos. Rectifica de sal y sirve.</t>
+          <t>1. Pica fina la cebolla, el puerro y el ajo. Sofríelos en una cazuela con el aceite a fuego medio unos 5 minutos, removiendo.
+2. Añade el magro, el tomate frito y el laurel. Aparta la cazuela del fuego un momento, echa el pimentón y remueve para que no se queme. Rehoga 5 minutos.
+3. Vierte el vino y deja que evapore un par de minutos. Añade el agua y la pastilla de caldo, y cuece tapado a fuego suave unos 15-20 minutos para que el magro empiece a ablandarse.
+4. Incorpora las patatas y las zanahorias, con más agua si hace falta para cubrirlas. Cuece tapado a fuego suave 20-25 minutos más, hasta que estén tiernas.
+5. Añade los guisantes escurridos, mezcla con cuidado y deja 2-3 minutos. Rectifica de sal y sirve.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>46301.58943972222</v>
+        <v>46301.59010552083</v>
       </c>
     </row>
     <row r="3">

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Menú semanal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -505,24 +505,77 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Fajipizza</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Cenas</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1 tortilla integral para fajitas
+Tomate natural
+Queso mozzarella
+Jamón cocido
+Orégano
+Orégano</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1. Precalienta el horno a 220 °C.
+2. Monta la “pizza”
+3. Mete en el horno durante 10 minutos</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Puedes incluir los ingredientes que prefieras. Recomendable el tomate especial pizza de Lidl (saludable)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>46301.59432833333</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>Guiso de patatas con magro</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Ana</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D3" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1 cebolla
 1 puerro
@@ -540,7 +593,7 @@
 100 g de guisantes en conserva</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Pica fina la cebolla, el puerro y el ajo. Sofríelos en una cazuela con el aceite a fuego medio unos 5 minutos, removiendo.
 2. Añade el magro, el tomate frito y el laurel. Aparta la cazuela del fuego un momento, echa el pimentón y remueve para que no se queme. Rehoga 5 minutos.
@@ -549,41 +602,41 @@
 5. Añade los guisantes escurridos, mezcla con cuidado y deja 2-3 minutos. Rectifica de sal y sirve.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Sustituto de la pastilla de caldo: usa 500-600 ml de caldo casero o de brik en lugar del agua y de la pastilla. Si no tienes caldo, sirve agua con una pizca extra de sal, una cucharadita de pimentón y el laurel</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>46301.59010552083</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Fiambre de pollo</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Desayunos</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>María</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D4" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1 pechuga pollo
 2 cucharadas aceite de oliva
@@ -595,7 +648,7 @@
 Pimienta negra (al gusto)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Mezclar en un bol todas las especias junto con el aceite
 2. Untar la pechuga de pollo con la mezcla y dejar reposar en un tupper al menos una hora
@@ -604,41 +657,41 @@
 5. Cuando esté listo, córtala en láminas muy finas y consérvala en un tupper</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Échale un chorro de limón una vez cortado</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>46301.42774069445</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Mousse de oreo con galleta María</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Postres</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Antonio</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D5" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>14 galletas maria
 Vaso de leche
@@ -646,7 +699,7 @@
 Nata de montar</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Meter galletas María y vaso de leche caliente  en trituradora
 2. Triturar
@@ -656,22 +709,22 @@
 6. Hacemos polvo otras galletas oreo y servimos encima</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/reel/DOER-GjCHru/?stkn=MWNjZjIwY2x4MXdtcQ==</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>46301.48902870371</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J4"/>
+  <autoFilter ref="A1:J5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Menú semanal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -619,24 +619,76 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Pimientos a la Cerdeña Style</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Comidas</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Martí</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4/5 pimientos Rojos / Amarillos (No VERDeS)
+1 diente de Ajo (entero)
+Aceitunas negras (con o sin hueso)
+Aceite
+Alcaparras (bajo sal)
+Anchoas (si tienes)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1. -hornear los pimientos (35/40) mins a 180º
+2. -Quitar la piel a todos los pimientos y cortar en líneas verticales
+3. - sofreír un diente de ajo entero con las alcaparras y las anchoas
+4. -añadir los pimientos
+5. -añadir las aceitunas
+6. -remover todo por 5/10 minutos y apaga</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>46301.78268822917</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>Fiambre de pollo</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Desayunos</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>María</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D5" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1 pechuga pollo
 2 cucharadas aceite de oliva
@@ -648,7 +700,7 @@
 Pimienta negra (al gusto)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Mezclar en un bol todas las especias junto con el aceite
 2. Untar la pechuga de pollo con la mezcla y dejar reposar en un tupper al menos una hora
@@ -657,41 +709,41 @@
 5. Cuando esté listo, córtala en láminas muy finas y consérvala en un tupper</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Échale un chorro de limón una vez cortado</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>46301.42774069445</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Mousse de oreo con galleta María</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Postres</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Antonio</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D6" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>14 galletas maria
 Vaso de leche
@@ -699,7 +751,7 @@
 Nata de montar</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Meter galletas María y vaso de leche caliente  en trituradora
 2. Triturar
@@ -709,22 +761,22 @@
 6. Hacemos polvo otras galletas oreo y servimos encima</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/reel/DOER-GjCHru/?stkn=MWNjZjIwY2x4MXdtcQ==</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>46301.48902870371</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J5"/>
+  <autoFilter ref="A1:J6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Menú semanal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -671,24 +671,77 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>Ragú</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Comidas</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Martí</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>500gr de carne picada (da igual el animal depende del gusto
+Medio vaso de Vino blanco
+1 cebolla
+Mucha albahaca
+Sal
+Pimienta
+1 vasito de tomate NATURAL
+1 vaso de agua</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1. Cortar la cebolla en cachos o muy pequeños o grandes en hojas (depende del gusto y sofreír con abundante aceite
+2. Después del sofrito añadir la carne picada y mezclar bien añadiendo el vasito de vino y la sal (a ojo)
+3. Echar el tomate natural todo
+4. Echar mucha albahaca y remover
+5. Añadir el vaso de agua y dejar a fuego bajo durante 3 horas</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>46301.78572765047</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>Fiambre de pollo</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Desayunos</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>María</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D6" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1 pechuga pollo
 2 cucharadas aceite de oliva
@@ -700,7 +753,7 @@
 Pimienta negra (al gusto)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Mezclar en un bol todas las especias junto con el aceite
 2. Untar la pechuga de pollo con la mezcla y dejar reposar en un tupper al menos una hora
@@ -709,41 +762,41 @@
 5. Cuando esté listo, córtala en láminas muy finas y consérvala en un tupper</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Échale un chorro de limón una vez cortado</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>46301.42774069445</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Mousse de oreo con galleta María</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Postres</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Antonio</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>14 galletas maria
 Vaso de leche
@@ -751,7 +804,7 @@
 Nata de montar</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Meter galletas María y vaso de leche caliente  en trituradora
 2. Triturar
@@ -761,22 +814,22 @@
 6. Hacemos polvo otras galletas oreo y servimos encima</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/reel/DOER-GjCHru/?stkn=MWNjZjIwY2x4MXdtcQ==</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <v>46301.48902870371</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J6"/>
+  <autoFilter ref="A1:J7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Menú semanal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -558,24 +558,56 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>Filete empanado Marta</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Comidas</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Martí</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>46301.78612304398</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>Guiso de patatas con magro</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Ana</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D4" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1 cebolla
 1 puerro
@@ -593,7 +625,7 @@
 100 g de guisantes en conserva</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Pica fina la cebolla, el puerro y el ajo. Sofríelos en una cazuela con el aceite a fuego medio unos 5 minutos, removiendo.
 2. Añade el magro, el tomate frito y el laurel. Aparta la cazuela del fuego un momento, echa el pimentón y remueve para que no se queme. Rehoga 5 minutos.
@@ -602,43 +634,43 @@
 5. Añade los guisantes escurridos, mezcla con cuidado y deja 2-3 minutos. Rectifica de sal y sirve.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Sustituto de la pastilla de caldo: usa 500-600 ml de caldo casero o de brik en lugar del agua y de la pastilla. Si no tienes caldo, sirve agua con una pizca extra de sal, una cucharadita de pimentón y el laurel</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>46301.59010552083</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Pimientos a la Cerdeña Style</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Martí</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D5" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>4/5 pimientos Rojos / Amarillos (No VERDeS)
 1 diente de Ajo (entero)
@@ -648,7 +680,7 @@
 Anchoas (si tienes)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. -hornear los pimientos (35/40) mins a 180º
 2. -Quitar la piel a todos los pimientos y cortar en líneas verticales
@@ -658,39 +690,39 @@
 6. -remover todo por 5/10 minutos y apaga</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>46301.78268822917</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Ragú</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Martí</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D6" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>500gr de carne picada (da igual el animal depende del gusto
 Medio vaso de Vino blanco
@@ -702,7 +734,7 @@
 1 vaso de agua</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Cortar la cebolla en cachos o muy pequeños o grandes en hojas (depende del gusto y sofreír con abundante aceite
 2. Después del sofrito añadir la carne picada y mezclar bien añadiendo el vasito de vino y la sal (a ojo)
@@ -711,37 +743,37 @@
 5. Añadir el vaso de agua y dejar a fuego bajo durante 3 horas</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>46301.78572765047</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Fiambre de pollo</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Desayunos</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>María</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D7" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1 pechuga pollo
 2 cucharadas aceite de oliva
@@ -753,7 +785,7 @@
 Pimienta negra (al gusto)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Mezclar en un bol todas las especias junto con el aceite
 2. Untar la pechuga de pollo con la mezcla y dejar reposar en un tupper al menos una hora
@@ -762,41 +794,41 @@
 5. Cuando esté listo, córtala en láminas muy finas y consérvala en un tupper</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Échale un chorro de limón una vez cortado</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <v>46301.42774069445</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Mousse de oreo con galleta María</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Postres</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Antonio</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D8" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>14 galletas maria
 Vaso de leche
@@ -804,7 +836,7 @@
 Nata de montar</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Meter galletas María y vaso de leche caliente  en trituradora
 2. Triturar
@@ -814,22 +846,22 @@
 6. Hacemos polvo otras galletas oreo y servimos encima</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/reel/DOER-GjCHru/?stkn=MWNjZjIwY2x4MXdtcQ==</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <v>46301.48902870371</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J7"/>
+  <autoFilter ref="A1:J8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Menú semanal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -590,24 +590,72 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Filete empanado Martí</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Comidas</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Martí</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>500gr de pollo del corral fileteado
+3 huevos
+Aceite virgen extra
+Ralladura para empanar de Maíz</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1. Batir los huevos con sal y pimienta
+2. Rebozar el pollo en el maíz
+3. Freír con aceite virgen extra
+4. Escurrir el filete en papel de cocina</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>46301.78760721064</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>Guiso de patatas con magro</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Ana</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D5" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1 cebolla
 1 puerro
@@ -625,7 +673,7 @@
 100 g de guisantes en conserva</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Pica fina la cebolla, el puerro y el ajo. Sofríelos en una cazuela con el aceite a fuego medio unos 5 minutos, removiendo.
 2. Añade el magro, el tomate frito y el laurel. Aparta la cazuela del fuego un momento, echa el pimentón y remueve para que no se queme. Rehoga 5 minutos.
@@ -634,43 +682,43 @@
 5. Añade los guisantes escurridos, mezcla con cuidado y deja 2-3 minutos. Rectifica de sal y sirve.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Sustituto de la pastilla de caldo: usa 500-600 ml de caldo casero o de brik en lugar del agua y de la pastilla. Si no tienes caldo, sirve agua con una pizca extra de sal, una cucharadita de pimentón y el laurel</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>46301.59010552083</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Pimientos a la Cerdeña Style</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Martí</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D6" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>4/5 pimientos Rojos / Amarillos (No VERDeS)
 1 diente de Ajo (entero)
@@ -680,7 +728,7 @@
 Anchoas (si tienes)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. -hornear los pimientos (35/40) mins a 180º
 2. -Quitar la piel a todos los pimientos y cortar en líneas verticales
@@ -690,39 +738,39 @@
 6. -remover todo por 5/10 minutos y apaga</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>46301.78268822917</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Ragú</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Martí</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D7" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>500gr de carne picada (da igual el animal depende del gusto
 Medio vaso de Vino blanco
@@ -734,7 +782,7 @@
 1 vaso de agua</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Cortar la cebolla en cachos o muy pequeños o grandes en hojas (depende del gusto y sofreír con abundante aceite
 2. Después del sofrito añadir la carne picada y mezclar bien añadiendo el vasito de vino y la sal (a ojo)
@@ -743,37 +791,37 @@
 5. Añadir el vaso de agua y dejar a fuego bajo durante 3 horas</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <v>46301.78572765047</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Fiambre de pollo</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Desayunos</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>María</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D8" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1 pechuga pollo
 2 cucharadas aceite de oliva
@@ -785,7 +833,7 @@
 Pimienta negra (al gusto)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Mezclar en un bol todas las especias junto con el aceite
 2. Untar la pechuga de pollo con la mezcla y dejar reposar en un tupper al menos una hora
@@ -794,41 +842,41 @@
 5. Cuando esté listo, córtala en láminas muy finas y consérvala en un tupper</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Échale un chorro de limón una vez cortado</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <v>46301.42774069445</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Mousse de oreo con galleta María</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Postres</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Antonio</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D9" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>14 galletas maria
 Vaso de leche
@@ -836,7 +884,7 @@
 Nata de montar</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Meter galletas María y vaso de leche caliente  en trituradora
 2. Triturar
@@ -846,22 +894,22 @@
 6. Hacemos polvo otras galletas oreo y servimos encima</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/reel/DOER-GjCHru/?stkn=MWNjZjIwY2x4MXdtcQ==</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J9" s="3" t="n">
         <v>46301.48902870371</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J8"/>
+  <autoFilter ref="A1:J9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Menú semanal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Filete empanado Marta</t>
+          <t>Filete empanado Martí</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -574,42 +574,10 @@
       <c r="D3" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>46301.78612304398</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Filete empanado Martí</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Comidas</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Martí</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="E3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>500gr de pollo del corral fileteado
 3 huevos
@@ -617,7 +585,7 @@
 Ralladura para empanar de Maíz</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Batir los huevos con sal y pimienta
 2. Rebozar el pollo en el maíz
@@ -625,37 +593,37 @@
 4. Escurrir el filete en papel de cocina</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>46301.78760721064</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Guiso de patatas con magro</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Ana</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D4" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1 cebolla
 1 puerro
@@ -673,7 +641,7 @@
 100 g de guisantes en conserva</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Pica fina la cebolla, el puerro y el ajo. Sofríelos en una cazuela con el aceite a fuego medio unos 5 minutos, removiendo.
 2. Añade el magro, el tomate frito y el laurel. Aparta la cazuela del fuego un momento, echa el pimentón y remueve para que no se queme. Rehoga 5 minutos.
@@ -682,43 +650,43 @@
 5. Añade los guisantes escurridos, mezcla con cuidado y deja 2-3 minutos. Rectifica de sal y sirve.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Sustituto de la pastilla de caldo: usa 500-600 ml de caldo casero o de brik en lugar del agua y de la pastilla. Si no tienes caldo, sirve agua con una pizca extra de sal, una cucharadita de pimentón y el laurel</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>46301.59010552083</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Pimientos a la Cerdeña Style</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Martí</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D5" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>4/5 pimientos Rojos / Amarillos (No VERDeS)
 1 diente de Ajo (entero)
@@ -728,7 +696,7 @@
 Anchoas (si tienes)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. -hornear los pimientos (35/40) mins a 180º
 2. -Quitar la piel a todos los pimientos y cortar en líneas verticales
@@ -738,39 +706,39 @@
 6. -remover todo por 5/10 minutos y apaga</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>46301.78268822917</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Ragú</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Martí</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D6" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>500gr de carne picada (da igual el animal depende del gusto
 Medio vaso de Vino blanco
@@ -782,7 +750,7 @@
 1 vaso de agua</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Cortar la cebolla en cachos o muy pequeños o grandes en hojas (depende del gusto y sofreír con abundante aceite
 2. Después del sofrito añadir la carne picada y mezclar bien añadiendo el vasito de vino y la sal (a ojo)
@@ -791,37 +759,37 @@
 5. Añadir el vaso de agua y dejar a fuego bajo durante 3 horas</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>46301.78572765047</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Fiambre de pollo</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Desayunos</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>María</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D7" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1 pechuga pollo
 2 cucharadas aceite de oliva
@@ -833,7 +801,7 @@
 Pimienta negra (al gusto)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Mezclar en un bol todas las especias junto con el aceite
 2. Untar la pechuga de pollo con la mezcla y dejar reposar en un tupper al menos una hora
@@ -842,41 +810,41 @@
 5. Cuando esté listo, córtala en láminas muy finas y consérvala en un tupper</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Échale un chorro de limón una vez cortado</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <v>46301.42774069445</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Mousse de oreo con galleta María</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Postres</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Antonio</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D8" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>14 galletas maria
 Vaso de leche
@@ -884,7 +852,7 @@
 Nata de montar</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Meter galletas María y vaso de leche caliente  en trituradora
 2. Triturar
@@ -894,22 +862,22 @@
 6. Hacemos polvo otras galletas oreo y servimos encima</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/reel/DOER-GjCHru/?stkn=MWNjZjIwY2x4MXdtcQ==</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <v>46301.48902870371</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J9"/>
+  <autoFilter ref="A1:J8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Menú semanal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -558,26 +558,73 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>Emulsión</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Comidas</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Martí</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Medio cuenco de aceite virgen extra
+1 pizca de sal
+Medio limón exprimido
+Pimienta
+Albahaca
+Tenedor</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1. Batir todos los ingredientes hasta que sea una crema /emulsion</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>46301.78938746528</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>Filete empanado Martí</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Martí</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D4" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>500gr de pollo del corral fileteado
 3 huevos
@@ -585,7 +632,7 @@
 Ralladura para empanar de Maíz</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Batir los huevos con sal y pimienta
 2. Rebozar el pollo en el maíz
@@ -593,37 +640,37 @@
 4. Escurrir el filete en papel de cocina</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>46301.78760721064</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Guiso de patatas con magro</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Ana</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D5" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1 cebolla
 1 puerro
@@ -641,7 +688,7 @@
 100 g de guisantes en conserva</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Pica fina la cebolla, el puerro y el ajo. Sofríelos en una cazuela con el aceite a fuego medio unos 5 minutos, removiendo.
 2. Añade el magro, el tomate frito y el laurel. Aparta la cazuela del fuego un momento, echa el pimentón y remueve para que no se queme. Rehoga 5 minutos.
@@ -650,43 +697,43 @@
 5. Añade los guisantes escurridos, mezcla con cuidado y deja 2-3 minutos. Rectifica de sal y sirve.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Sustituto de la pastilla de caldo: usa 500-600 ml de caldo casero o de brik en lugar del agua y de la pastilla. Si no tienes caldo, sirve agua con una pizca extra de sal, una cucharadita de pimentón y el laurel</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>46301.59010552083</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Pimientos a la Cerdeña Style</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Martí</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D6" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>4/5 pimientos Rojos / Amarillos (No VERDeS)
 1 diente de Ajo (entero)
@@ -696,7 +743,7 @@
 Anchoas (si tienes)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. -hornear los pimientos (35/40) mins a 180º
 2. -Quitar la piel a todos los pimientos y cortar en líneas verticales
@@ -706,39 +753,39 @@
 6. -remover todo por 5/10 minutos y apaga</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>46301.78268822917</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Ragú</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Martí</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D7" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>500gr de carne picada (da igual el animal depende del gusto
 Medio vaso de Vino blanco
@@ -750,7 +797,7 @@
 1 vaso de agua</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Cortar la cebolla en cachos o muy pequeños o grandes en hojas (depende del gusto y sofreír con abundante aceite
 2. Después del sofrito añadir la carne picada y mezclar bien añadiendo el vasito de vino y la sal (a ojo)
@@ -759,37 +806,37 @@
 5. Añadir el vaso de agua y dejar a fuego bajo durante 3 horas</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <v>46301.78572765047</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Fiambre de pollo</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Desayunos</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>María</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D8" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1 pechuga pollo
 2 cucharadas aceite de oliva
@@ -801,7 +848,7 @@
 Pimienta negra (al gusto)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Mezclar en un bol todas las especias junto con el aceite
 2. Untar la pechuga de pollo con la mezcla y dejar reposar en un tupper al menos una hora
@@ -810,41 +857,41 @@
 5. Cuando esté listo, córtala en láminas muy finas y consérvala en un tupper</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Échale un chorro de limón una vez cortado</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <v>46301.42774069445</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Mousse de oreo con galleta María</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Postres</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Antonio</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D9" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>14 galletas maria
 Vaso de leche
@@ -852,7 +899,7 @@
 Nata de montar</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Meter galletas María y vaso de leche caliente  en trituradora
 2. Triturar
@@ -862,22 +909,22 @@
 6. Hacemos polvo otras galletas oreo y servimos encima</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/reel/DOER-GjCHru/?stkn=MWNjZjIwY2x4MXdtcQ==</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J9" s="3" t="n">
         <v>46301.48902870371</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J8"/>
+  <autoFilter ref="A1:J9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Menú semanal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -605,26 +605,56 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Fideua con chipirones</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Comidas</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>46301.83050577546</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>Filete empanado Martí</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Martí</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D5" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E5" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>500gr de pollo del corral fileteado
 3 huevos
@@ -632,7 +662,7 @@
 Ralladura para empanar de Maíz</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Batir los huevos con sal y pimienta
 2. Rebozar el pollo en el maíz
@@ -640,37 +670,37 @@
 4. Escurrir el filete en papel de cocina</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>46301.78760721064</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Guiso de patatas con magro</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Ana</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D6" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1 cebolla
 1 puerro
@@ -688,7 +718,7 @@
 100 g de guisantes en conserva</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Pica fina la cebolla, el puerro y el ajo. Sofríelos en una cazuela con el aceite a fuego medio unos 5 minutos, removiendo.
 2. Añade el magro, el tomate frito y el laurel. Aparta la cazuela del fuego un momento, echa el pimentón y remueve para que no se queme. Rehoga 5 minutos.
@@ -697,43 +727,43 @@
 5. Añade los guisantes escurridos, mezcla con cuidado y deja 2-3 minutos. Rectifica de sal y sirve.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Sustituto de la pastilla de caldo: usa 500-600 ml de caldo casero o de brik en lugar del agua y de la pastilla. Si no tienes caldo, sirve agua con una pizca extra de sal, una cucharadita de pimentón y el laurel</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>46301.59010552083</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Pimientos a la Cerdeña Style</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Martí</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D7" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>4/5 pimientos Rojos / Amarillos (No VERDeS)
 1 diente de Ajo (entero)
@@ -743,7 +773,7 @@
 Anchoas (si tienes)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. -hornear los pimientos (35/40) mins a 180º
 2. -Quitar la piel a todos los pimientos y cortar en líneas verticales
@@ -753,39 +783,39 @@
 6. -remover todo por 5/10 minutos y apaga</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <v>46301.78268822917</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Ragú</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Martí</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D8" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>500gr de carne picada (da igual el animal depende del gusto
 Medio vaso de Vino blanco
@@ -797,7 +827,7 @@
 1 vaso de agua</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Cortar la cebolla en cachos o muy pequeños o grandes en hojas (depende del gusto y sofreír con abundante aceite
 2. Después del sofrito añadir la carne picada y mezclar bien añadiendo el vasito de vino y la sal (a ojo)
@@ -806,37 +836,37 @@
 5. Añadir el vaso de agua y dejar a fuego bajo durante 3 horas</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <v>46301.78572765047</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Fiambre de pollo</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Desayunos</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>María</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D9" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1 pechuga pollo
 2 cucharadas aceite de oliva
@@ -848,7 +878,7 @@
 Pimienta negra (al gusto)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Mezclar en un bol todas las especias junto con el aceite
 2. Untar la pechuga de pollo con la mezcla y dejar reposar en un tupper al menos una hora
@@ -857,41 +887,41 @@
 5. Cuando esté listo, córtala en láminas muy finas y consérvala en un tupper</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Échale un chorro de limón una vez cortado</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J9" s="3" t="n">
         <v>46301.42774069445</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Mousse de oreo con galleta María</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Postres</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Antonio</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D10" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>14 galletas maria
 Vaso de leche
@@ -899,7 +929,7 @@
 Nata de montar</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1. Meter galletas María y vaso de leche caliente  en trituradora
 2. Triturar
@@ -909,22 +939,22 @@
 6. Hacemos polvo otras galletas oreo y servimos encima</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/reel/DOER-GjCHru/?stkn=MWNjZjIwY2x4MXdtcQ==</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>46301.48902870371</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J9"/>
+  <autoFilter ref="A1:J10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -618,9 +618,26 @@
           <t>María</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
+      <c r="D4" s="2" t="n">
+        <v>120</v>
+      </c>
       <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Chipirones
+Gambas
+Caldo de pescado
+Fideos de Fideua
+Tomate triturado
+Cebolla morada
+Ajo
+Vino tinto
+Azafrán
+Sal
+Aceite
+Mucho amor</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
@@ -629,7 +646,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>46301.83050577546</v>
+        <v>46301.83209763889</v>
       </c>
     </row>
     <row r="5">

--- a/recetas.xlsx
+++ b/recetas.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Menú semanal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recetas'!$A$1:$J$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -813,26 +813,83 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>Puré de calabaza</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Comidas</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2 calabacines
+500g calabaza
+1 cebolla
+2 puerros
+2 patatas
+4 zanahorias
+6 quesitos
+1 trozo jamón
+Pimienta
+Sal
+Aceite</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1. Echar aceite en la olla y sofreír la cebolla y el puerro
+2. Cuando la cebolla y el puerro estén, echar el resto de verduras, sal y pimienta y sofreír dos minutos
+3. Cubrir con agua toda la verdura
+4. Dejar cocer aproximadamente 1h hasta que toda la verdura esté blanda
+5. Echar el trozo de jamón y dejarlo cocer 10 minutos más
+6. Echar los quesitos hasta que se deshagan y batir todo</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>46304.98342508102</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>Ragú</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Comidas</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Martí</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D9" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>500gr de carne picada (da igual el animal depende del gusto
 Medio vaso de Vino blanco
@@ -844,7 +901,7 @@
 1 vaso de agua</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Cortar la cebolla en cachos o muy pequeños o grandes en hojas (depende del gusto y sofreír con abundante aceite
 2. Después del sofrito añadir la carne picada y mezclar bien añadiendo el vasito de vino y la sal (a ojo)
@@ -853,37 +910,37 @@
 5. Añadir el vaso de agua y dejar a fuego bajo durante 3 horas</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J9" s="3" t="n">
         <v>46301.78572765047</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Fiambre de pollo</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Desayunos</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>María</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D10" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1 pechuga pollo
 2 cucharadas aceite de oliva
@@ -895,7 +952,7 @@
 Pimienta negra (al gusto)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1. Mezclar en un bol todas las especias junto con el aceite
 2. Untar la pechuga de pollo con la mezcla y dejar reposar en un tupper al menos una hora
@@ -904,41 +961,41 @@
 5. Cuando esté listo, córtala en láminas muy finas y consérvala en un tupper</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Échale un chorro de limón una vez cortado</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>46301.42774069445</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Mousse de oreo con galleta María</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Postres</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Antonio</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D11" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>14 galletas maria
 Vaso de leche
@@ -946,7 +1003,7 @@
 Nata de montar</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1. Meter galletas María y vaso de leche caliente  en trituradora
 2. Triturar
@@ -956,22 +1013,22 @@
 6. Hacemos polvo otras galletas oreo y servimos encima</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/reel/DOER-GjCHru/?stkn=MWNjZjIwY2x4MXdtcQ==</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="J11" s="3" t="n">
         <v>46301.48902870371</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J10"/>
+  <autoFilter ref="A1:J11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
